--- a/小野町_引継ぎ_整理済/08_協議会資料/小野町_交付金_福島県の得点分析_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/08_協議会資料/小野町_交付金_福島県の得点分析_20260925.xlsx
@@ -2534,7 +2534,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>全国該当率が6割以上で福島県が0点の項目（大雪地区広域連合の方法による）</t>
+          <t>全国該当率が6割以上で福島県が0点の項目（他団体の方法による）</t>
         </is>
       </c>
     </row>
